--- a/01_경혈별_해부생리_분석보고서/LI_수양명대장경/LI04_합곡/LI04_합곡_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/LI_수양명대장경/LI04_합곡/LI04_합곡_해부생리_분석데이터.xlsx
@@ -11,16 +11,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.문헌스크리닝" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.원천_재인용" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.이명_KJH" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.FMA_Layer별(T2)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.FMA_Layer별(T3)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.자침깊이_계산" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.교재비교" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.분기계통" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.분기추론_TriTarget" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.LayerA_LI4확인" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.BCheck_T2이중채점" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.BCheck_T3이중채점" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.외부검색로그" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.주치분리" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.ARI_T1이중채점" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.ARI_T2이중채점" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.ARI_T1≡2이중채점" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.ARI_T3이중채점" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.S_orig_하위항목" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부록A.FMA_해부실체" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="17" state="visible" r:id="rId17"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -464,7 +464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Target (Tri-Target)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T1 고전(第1·2掌骨底 결합부 앞)</t>
+          <t>Target 1≡2 고전 문헌·촉진(第1·2掌骨底 결합부 앞, 구 T1)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T2 현대(第2掌骨 노쪽 중점)</t>
+          <t>Target 3 WHO·현대(第2掌骨 노쪽 중점, 구 T2)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -596,18 +596,11 @@
           <t>ΔARI-Core</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7.5 (&lt;10 → 병기)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>7.5 (&lt;10 → 병기, Tri-Target 규칙)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -620,13 +613,18 @@
           <t>⚠ 임부 금침 문헌(《铜人》 이래) — SI와 별도</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Framework 2.7.7 재검</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>점수 불변 — 위치 불변으로 구판 이중 채점 승계, S_orig ④ 《通考》·《经络通鉴》 교감 재검 결과 단계 불변(75)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -655,7 +653,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>T2 (현대 정위)</t>
+          <t>Target 3 (WHO 정위, 구 T2)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -1222,7 +1220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.7" customWidth="1" min="1" max="1"/>
@@ -1264,7 +1262,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>열병 무한(無汗)·한열·학질</t>
+          <t>열병으로 땀이 나지 않음·한열·해학</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1281,7 +1279,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>비뉵·눈 질환·두통·치통</t>
+          <t>콧물·코피, 눈이 침침하고 아파 뜨지 못함, 두통, 충치 통증</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1298,7 +1296,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>구금·순문불수·실음</t>
+          <t>입술이 다물어지지 않음, 목이 쉬어 말을 못 하고 입을 악물어 벌리지 못함, 풍으로 목소리를 잃음</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1315,7 +1313,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>이롱·후비·면종</t>
+          <t>귀가 먹고 귓속이 막힘·후비·얼굴이 붓는 것</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1332,7 +1330,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>비위(痱痿)·팔목 불용</t>
+          <t>비(痱)·위(痿)로 팔과 손목을 쓰지 못함</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1366,7 +1364,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>산후 맥절·태상창심</t>
+          <t>산후에 맥이 끊어짐, 태아가 위로 치밀어 가슴을 찌름(胎上搶心)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1491,6 +1489,23 @@
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>"手连肩脊痛难忍，合谷针时要太冲"(《席弘赋》, [通考] L963)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>주</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>《证治通鉴》 한국어 기술 기준</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴_04_第壹编_第七篇_手太阴肺经_手阳明大肠经_足阳明胃经_한글번역.md L415~460 (원문은 기준 텍스트로 인용)</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1534,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>하위 점수 — T1 (고전)</t>
+          <t>하위 점수 — Target 1≡2 (고전 문헌·촉진 실체화, 구 T1)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -1615,7 +1630,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>A: B1-01·papers.id 2054로 노동맥·첫째 등쪽뼈사이근 위치는 확인 가능하나 교재 기재 없음(50). B: 교재·실측 모두 결여, 추론만(25). 조정: 표준 해부서(B1)와 영상 종설(2054)이 T1의 핵심 표지(노동맥)를 확인하므로 추론만은 아님 → 50</t>
+          <t>A: B1-01·papers.id 2054로 노동맥·첫째 등쪽뼈사이근 위치는 확인 가능하나 교재 기재 없음(50). B: 교재·실측 모두 결여, 추론만(25). 조정: 표준 해부서(B1)와 영상 종설(2054)이 Target 1≡2의 핵심 표지(노동맥)를 확인하므로 추론만은 아님 → 50</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1647,12 +1662,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>T1 위치를 특정한 Layer A 없음. LI4 연구 일반을 유추하면 B-Check 6 → "동물 연구만/B-Check 6~7" 단계</t>
+          <t>Target 1≡2 위치를 특정한 Layer A 없음. LI4 연구 일반을 유추하면 B-Check 6 → "동물 연구만/B-Check 6~7" 단계</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>8절 T1</t>
+          <t>8절 Target 1≡2</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1728,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>하위 점수 — T2 (현대)</t>
+          <t>하위 점수 — Target 3 (WHO, 구 T2)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -1924,22 +1939,22 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>T1 A</t>
+          <t>Target 1≡2 A</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>T1 B</t>
+          <t>Target 1≡2 B</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>T2 A</t>
+          <t>Target 3 A</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>T2 B</t>
+          <t>Target 3 B</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -1976,7 +1991,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>《灵枢》 "大指岐骨之间"과 《明堂》 3푼은 한대 기술이나 범위형. T2 위치는 한대 기술이 직접 지정하지 않음(1964년 이후 정위)</t>
+          <t>《灵枢》 "大指岐骨之间"과 《明堂》 3푼은 한대 기술이나 범위형. Target 3 위치는 한대 기술이 직접 지정하지 않음(1964년 이후 정위)</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2023,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>송~청·근대(1955~1964) 문헌 대부분이 '岐骨间 陷中/动脉'(T1). T2는 2판 강의 이후 교재·국표에 한정. A·B 차는 '一寸五分'·'正中点' 등 이문의 비중 판단 차이</t>
+          <t>송~청·근대(1955~1964) 문헌 대부분이 '岐骨间 陷中/动脉'(Target 1≡2). Target 3은 2판 강의 이후 교재·국표에 한정. A·B 차는 '一寸五分'·'正中点' 등 이문의 비중 판단 차이</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2062,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>④ 《通考》 교감</t>
+          <t>④ 《通考》·《经络通鉴》 교감</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2072,7 +2087,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>虎口 오분류 교정, 上合谷=古합곡 판정, 국표 2006 '第1、2掌骨间' 삭제 비판</t>
+          <t>《通考》: 虎口 오분류 교정, 上合谷=古합곡 판정, 국표 2006 '第1、2掌骨间' 삭제 비판. 《经络通鉴》 재검(2026-10-25): 手阳明 맥구=합곡~양계 맥동처, 古穴名 '手阳明'=합곡(中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L733·1121), 경맥 전체 확장 해석 비판(L253·287) — 새 전사 오류 교정 없음 → 단계 불변(75)</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2809,6 +2824,94 @@
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 1절</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>3대 원전</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>4대 원전, 《经络通鉴》 행 5개(포인터: 中国针灸经络通鉴_18_第叁编_第二篇_手阳明经脉、经别、络脉和经筋.md L90·110·162·217·273; 中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L235·253·287·452·573·733·1121; 中国针灸经络通鉴_37_第伍编_附篇一_脉名索引.md L55·361·365)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>정본 1절·Rank 1 &amp; 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 1·9절 证治</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>자체 요약어</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>한글번역 문장으로 기술(中国针灸证治通鉴_04_第壹编_第七篇_手太阴肺经_手阳明大肠经_足阳明胃经_한글번역.md L423·445·457), 瞶目/䁾目 차이 기록</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>정본 Rank 1 &amp; 2 《证治通鉴》 원칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 4·7절</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Dual-Target T1 vs T2</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Tri-Target 좌표·쌍별 Δ(T1–T2 ≤5mm 병합; T1–T3·T2–T3 20~30mm 분기, 모두 추정), Target 2 자입 기준점, 구 T1→Target 1≡2·구 T2→Target 3, 시트 7 재작성·시트명 T1/T2→T1≡2/T3</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>정본 Rank 5 Tri-Target(Δ &gt; 10mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 10절</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>S_orig ④ 《通考》 교감</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>④ 《通考》·《经络通鉴》 교감 재검 — 단계 불변 75, ARI 점수 불변(61.25 ± 1.25 C / 68.75 ± 1.25 C)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>정본 Rank 7</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2835,7 +2938,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>1. 문헌 스크리닝 표 (3대 원전 원문 발췌)</t>
+          <t>1. 문헌 스크리닝 표 (4대 원전 원문 발췌)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -2948,7 +3051,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>T1 정위</t>
+          <t>Target 1≡2 정위</t>
         </is>
       </c>
     </row>
@@ -2970,7 +3073,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>T1 표지</t>
+          <t>Target 2(촉진 실체화) 표지</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3222,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>비뉵·무한 열병·눈·두통·치통·구금·후비·면종</t>
+          <t>(한글번역) 콧물이 흐르고 코피가 나며, 열병으로 땀이 나지 않고, 눈이 침침하며 눈이 아파 뜨지 못하고, 두통·충치 통증, 해학·한열, 비·위로 팔과 손목을 쓰지 못함, 입술이 다물어지지 않음, 광역, 목이 쉬어 말을 못 하고 입을 악물어 벌리지 못함, 귀가 먹고 귓속이 막힘, 후비, 얼굴이 붓는 것 — 中国针灸证治通鉴_04_第壹编_第七篇_手太阴肺经_手阳明大肠经_足阳明胃经_한글번역.md L423</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>$P_{single}$ 근거(9절)</t>
+          <t>$P_{single}$ 근거(9절). 한글번역 편 인용 원문은 瞶目→䁾目(원문 기준 텍스트를 따름)</t>
         </is>
       </c>
     </row>
@@ -3141,12 +3244,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>산후·실음</t>
+          <t>(한글번역) 산후에 맥이 끊어지는 것, 태아가 위로 치밀어 가슴을 찌르는 것, 후비, 심번, 번열이 나고 머리가 아픈 것 / 풍으로 목소리를 잃어 말하지 못하는 것 — 中国针灸证治通鉴_04_第壹编_第七篇_手太阴肺经_手阳明大肠经_足阳明胃经_한글번역.md L445·457</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>9절</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>《灵枢·经脉》 "出合谷两骨之间，上入两筋之中" / 杨上善注 "掌骨及大指本节，表两骨之间也" / "合谷，在大指次指后岐骨间" / "合谷者，本经穴也，俗名虎口" — 中国针灸经络通鉴_18_第叁编_第二篇_手阳明经脉、经别、络脉和经筋.md L90·110·217·162</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>수양명 경맥 순행. 합곡 자리는 岐骨 사이 범위형 기술뿐</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>경맥 순행 기술. 혈위 정위에 새 정보 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>王冰注 "手阳明脉：在手大指次指歧骨间，合谷之分，动应于手也" / 표1-1 手阳明 脉口 "合谷至阳溪处" / "'手阳明'相当于合谷、阳溪穴之间的脉动处" — 中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L235·452·733</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>수양명 맥구 = 합곡~양계 맥동처; 경맥혈 '手阳明'은 맥구에서 나옴</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Target 2(촉진 실체화) 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>"这里的'阳明之脉'是指……阳明脉口，而不是……整条手足阳明经脉" / "以往人们都想当然地理解为……整个手阳明经脉" — 中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L253·287</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>고대 침방 '手阳明' = 손목 맥구. 경맥 전체 확장 해석 비판</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rank 4 경락론적 확장 비판; 9절</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>《千金翼方》 "'手阳明'穴在'大指奇后'（相当于'合谷'穴）" / 표1-1② 《圣惠方》 "虎口曲纹头" — 中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L1121·573</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>古穴名 '手阳明' = 합곡</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>3절 이명 보강</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>脉名索引 ◇手阳明·◇手阳明脉·◇大肠手阳明之脉 (쪽 번호 색인) — 中国针灸经络通鉴_37_第伍编_附篇一_脉名索引.md L55·361·365</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>색인(쪽 번호)만 있음 — 혈위 직접 정보 없음</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>검색 범위 기록</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3374,7 +3587,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>고전 정위 계승(T1) — [通鉴] L1060·1062</t>
+          <t>고전 정위 계승(Target 1≡2) — [通鉴] L1060·1062</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3609,29 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>정위 이동(T2), 국표 2006 '第1、2掌骨间' 삭제 — [通考] L667·767·773</t>
+          <t>정위 이동(Target 3), 국표 2006 '第1、2掌骨间' 삭제 — [通考] L667·767·773</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>선진·한대(보충)</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>《灵枢·经脉》</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>"出合谷两骨之间，上入两筋之中"</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>경맥 순행 기술(혈위 정위 아님) — 中国针灸经络通鉴_18_第叁编_第二篇_手阳明经脉、经别、络脉和经筋.md L90; 王冰注 행 보강 — 中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L235·253</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3793,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>古합곡(T1)과 같은 자리, 별혈로 오인 — [通考] L705·709</t>
+          <t>古합곡(Target 1≡2)과 같은 자리, 별혈로 오인 — [通考] L705·709</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3815,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>현대 합곡(T2) 자리, 자법만 다름 — [通考] L707·709</t>
+          <t>현대 합곡(Target 3) 자리, 자법만 다름 — [通考] L707·709</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3866,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>4. 3D 공간 좌표 및 Layer 1~5 층차 구조도</t>
+          <t>4. 3D 공간 좌표(자입 기준점 포함) 및 Layer 1~5 층차 구조도 — FMA 대조(Target 3, 구 T2)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -3978,7 +4213,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>도달 Layer(T2 추정)</t>
+          <t>도달 Layer(Target 3 추정)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -4442,18 +4677,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="48.40000000000001" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>7. 공간 변위 분기 추론도</t>
+          <t>7. 공간 변위 분기 추론도 (Tri-Target, 분기 기준 Δ &gt; 10mm)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -4462,68 +4700,299 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>계통</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>정의·근거</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>위치</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>포인터</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>① 고전 (T1)</t>
+          <t>Target 1 고전 문헌 위치</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>《灵枢》 "大指岐骨之间"; 송~명 "岐骨间陷中", 窦太师 "动脉应手", 《圣惠》 "后一寸五分"; 承淡安(1955)·1957 南京·1판 강의</t>
+          <t>《灵枢·本输》 "在大指岐骨之间"; 《明堂》 "手大指岐骨间"</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>第1·2掌骨底 결합부 바로 먼쪽 오목(노동맥 손등 촉지점) — [通考] L775</t>
+          <t>첫째·둘째 손허리뼈 사이</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>두 손허리뼈가 갈라지는 岐骨 사이(범위형, 손허리뼈 바닥 결합부 앞)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3푼(6.9mm)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[通考] L681·683; 中国针灸经络通鉴_18_第叁编_第二篇_手阳明经脉、经别、络脉和经筋.md L273</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>② 중간형</t>
+          <t>Target 2 촉진 실체화 위치(자입 기준점)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>1959 上海第一医学院</t>
+          <t>"动应于手"(王冰注), "陷中"(《铜人》), "歧骨缝中，动脉应手"(《玉龙经》) → 노동맥 손등 촉지점</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>둘째 손허리뼈 노쪽 가장자리 근위 1/3 — [通考] L701</t>
+          <t>첫째·둘째 손허리뼈 바닥 사이 골극 중앙(둘째 손허리뼈 쪽)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>두 손허리뼈 바닥 결합부 바로 먼쪽 오목</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3푼(6.9mm), 동맥과 같은 층</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[通考] L775; 中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L235·733; B1-01; papers.id 2054. 경계: 둘째·첫째 손허리뼈 바닥, 첫째 등쪽뼈사이근(FMA:37424) 두 갈래 사이, 노동맥(FMA:22730) 통과, 긴엄지폄근 힘줄(FMA ID 보고서 표 밖)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>③ 현대 (T2)</t>
+          <t>Target 3 현대 WHO 위치</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2판 강의(1964)~7판, 국표 1990/2006</t>
+          <t>WHO 2008·국표 2006 "第2掌骨桡侧的中点"</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>둘째 손허리뼈 노쪽 중점 — [通考] L667·773</t>
+          <t>둘째 손허리뼈 노쪽 가장자리</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>둘째 손허리뼈 중점</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5~10푼(11.5~23mm)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[通考] L667·773</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>(참고) 1959 上海 중간형</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>"第二掌骨桡侧缘近侧1/3与远侧2/3交界处"</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>둘째 손허리뼈 노쪽 가장자리</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Target 3에서 약 1cm 몸쪽(추정)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[通考] L701 — Tri-Target 정의 밖</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>쌍별 편차표 (모두 추정, 실측 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>쌍</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Δ (추정)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>추정 근거</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Target 1 – Target 2</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>약 5mm 이내</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>《通考》 L775가 고전 위치를 노동맥 손등 촉지점(第1、2掌骨底交叉的骨缝)과 같은 곳으로 판정; 차이는 범위형 기술의 폭뿐</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>≤ 10mm → 병합(Target 1≡2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Target 1 – Target 3</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>약 20~30mm</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>둘째 손허리뼈 길이(약 6~7cm, B1-01 가정)의 절반 가까이</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>&gt; 10mm → 분기</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Target 2 – Target 3</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>약 20~30mm</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>같은 근거; 《通考》 "此处已不能触及动脉搏动"(L775)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>&gt; 10mm → 분기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Target 1≡2 vs Target 3</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>독립 Target 2개 — 10절에서 각각 이중 채점</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ΔARI-Core 7.5 &lt; 10 → 병기(단독 우위 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>구판 대응</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>구 T1(고전) → Target 1≡2; 구 T2(현대 국표) → Target 3</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>위치 불변 → 기존 채점자 A·B 이중 채점 승계</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Target 2는 새 독립 Target 아님</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5666,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>종설(T1 해부 근거)</t>
+          <t>종설(Target 1≡2 해부 근거)</t>
         </is>
       </c>
     </row>
